--- a/artfynd/A 54835-2025 artfynd.xlsx
+++ b/artfynd/A 54835-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130018001</v>
       </c>
       <c r="B2" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54835-2025 artfynd.xlsx
+++ b/artfynd/A 54835-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130018001</v>
       </c>
       <c r="B2" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54835-2025 artfynd.xlsx
+++ b/artfynd/A 54835-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130018001</v>
       </c>
       <c r="B2" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54835-2025 artfynd.xlsx
+++ b/artfynd/A 54835-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130018001</v>
       </c>
       <c r="B2" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54835-2025 artfynd.xlsx
+++ b/artfynd/A 54835-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,46 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130018001</v>
+        <v>130017983</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>653939</v>
+        <v>653988</v>
       </c>
       <c r="R2" t="n">
-        <v>6683419</v>
+        <v>6683497</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,12 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Minst! Räknar en och en till 50 plantor och har då täckt knappt halva ytan.</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,6 +791,249 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>116072891</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Fågelsmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>653900</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6683352</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-04-18</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-04-18</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130018001</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>653939</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6683419</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Minst! Räknar en och en till 50 plantor och har då täckt knappt halva ytan.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54835-2025 artfynd.xlsx
+++ b/artfynd/A 54835-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130017983</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116072891</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1034,8 +1049,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130018001</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>